--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.41197032727464</v>
+        <v>13.39194517818213</v>
       </c>
       <c r="D2" t="n">
-        <v>79.94529379519473</v>
+        <v>12.99111024171914</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F2" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.48435319013499</v>
+        <v>6.578707393396936</v>
       </c>
       <c r="D3" t="n">
-        <v>72.09247903910254</v>
+        <v>11.71502784385416</v>
       </c>
       <c r="E3" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F3" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.8611816753442</v>
+        <v>11.35244202224343</v>
       </c>
       <c r="D4" t="n">
-        <v>63.67299270491375</v>
+        <v>10.34686131454849</v>
       </c>
       <c r="E4" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F4" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.31392507846864</v>
+        <v>6.388512825251153</v>
       </c>
       <c r="D5" t="n">
-        <v>55.55642648041913</v>
+        <v>9.027919303068108</v>
       </c>
       <c r="E5" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F5" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.9945986232221</v>
+        <v>9.261622276273592</v>
       </c>
       <c r="D6" t="n">
-        <v>71.59135123269378</v>
+        <v>11.63359457531274</v>
       </c>
       <c r="E6" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F6" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.92145499836562</v>
+        <v>4.374736437234414</v>
       </c>
       <c r="D7" t="n">
-        <v>19.12373185812346</v>
+        <v>3.107606426945062</v>
       </c>
       <c r="E7" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F7" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.88208916079598</v>
+        <v>7.293339488629346</v>
       </c>
       <c r="D8" t="n">
-        <v>42.18860175348112</v>
+        <v>6.855647784940682</v>
       </c>
       <c r="E8" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F8" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.26802843379501</v>
+        <v>8.656054620491689</v>
       </c>
       <c r="D9" t="n">
-        <v>56.40978962295552</v>
+        <v>9.166590813730272</v>
       </c>
       <c r="E9" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F9" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.33695835214066</v>
+        <v>4.929755732222857</v>
       </c>
       <c r="D10" t="n">
-        <v>30.25226631460982</v>
+        <v>4.915993276124095</v>
       </c>
       <c r="E10" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F10" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.64969891986771</v>
+        <v>3.518076074478503</v>
       </c>
       <c r="D11" t="n">
-        <v>21.29293986323452</v>
+        <v>3.460102727775609</v>
       </c>
       <c r="E11" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F11" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.95561338432821</v>
+        <v>5.030287174953335</v>
       </c>
       <c r="D12" t="n">
-        <v>16.62531908168686</v>
+        <v>2.701614350774115</v>
       </c>
       <c r="E12" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F12" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.52855176364099</v>
+        <v>9.023389661591661</v>
       </c>
       <c r="D13" t="n">
-        <v>32.92209284858519</v>
+        <v>5.349840087895094</v>
       </c>
       <c r="E13" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F13" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.65595923919642</v>
+        <v>8.231593376369419</v>
       </c>
       <c r="D14" t="n">
-        <v>18.67742606543616</v>
+        <v>3.035081735633376</v>
       </c>
       <c r="E14" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F14" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>59.94576851988738</v>
+        <v>9.7411873844817</v>
       </c>
       <c r="D15" t="n">
-        <v>18.78024309917732</v>
+        <v>3.051789503616315</v>
       </c>
       <c r="E15" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F15" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>70.23822533281383</v>
+        <v>11.41371161658225</v>
       </c>
       <c r="D16" t="n">
-        <v>25.89312794225466</v>
+        <v>4.207633290616383</v>
       </c>
       <c r="E16" t="n">
-        <v>17.01461664697542</v>
+        <v>2.764875205133506</v>
       </c>
       <c r="F16" t="n">
-        <v>21.96892032759079</v>
+        <v>3.569949553233503</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
